--- a/output/pdf_financials_xlsx/VPI.xlsx
+++ b/output/pdf_financials_xlsx/VPI.xlsx
@@ -1303,58 +1303,58 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.286839</v>
+        <v>-0.286839</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.252789</v>
+        <v>-0.252789</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.227441</v>
+        <v>-0.227441</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.184883</v>
+        <v>-0.184883</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.168084</v>
+        <v>-0.168084</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.184774</v>
+        <v>-0.184774</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.177712</v>
+        <v>-0.177712</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.216566</v>
+        <v>-0.216566</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.161213</v>
+        <v>-0.161213</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.027468</v>
+        <v>-0.027468</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.179918</v>
+        <v>-0.179918</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.616638</v>
+        <v>-0.616638</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.537265</v>
+        <v>-0.537265</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>0.269038</v>
+        <v>-0.269038</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>0.146063</v>
+        <v>-0.146063</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.048456</v>
+        <v>-0.048456</v>
       </c>
     </row>
     <row r="17">
@@ -1619,58 +1619,58 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.286839</v>
+        <v>-0.286839</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.252789</v>
+        <v>-0.252789</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.227441</v>
+        <v>-0.227441</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.184883</v>
+        <v>-0.184883</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.168084</v>
+        <v>-0.168084</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.184774</v>
+        <v>-0.184774</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.177712</v>
+        <v>-0.177712</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.216566</v>
+        <v>-0.216566</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.161213</v>
+        <v>-0.161213</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.027468</v>
+        <v>-0.027468</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.179918</v>
+        <v>-0.179918</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.616638</v>
+        <v>-0.616638</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.537265</v>
+        <v>-0.537265</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>0.269038</v>
+        <v>-0.269038</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>0.146063</v>
+        <v>-0.146063</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>0.048456</v>
+        <v>-0.048456</v>
       </c>
     </row>
     <row r="21">
@@ -1802,58 +1802,58 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.286839</v>
+        <v>-0.286839</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.252789</v>
+        <v>-0.252789</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.227441</v>
+        <v>-0.227441</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.184883</v>
+        <v>-0.184883</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.168084</v>
+        <v>-0.168084</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.184774</v>
+        <v>-0.184774</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.177712</v>
+        <v>-0.177712</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.216566</v>
+        <v>-0.216566</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.161213</v>
+        <v>-0.161213</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.027468</v>
+        <v>-0.027468</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.179918</v>
+        <v>-0.179918</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.616638</v>
+        <v>-0.616638</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.537265</v>
+        <v>-0.537265</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>0.269038</v>
+        <v>-0.269038</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>0.146063</v>
+        <v>-0.146063</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>0.048456</v>
+        <v>-0.048456</v>
       </c>
     </row>
     <row r="24">
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="O26" s="3" t="n">
-        <v>30.8319</v>
+        <v>-30.8319</v>
       </c>
       <c r="P26" s="1" t="inlineStr">
         <is>
@@ -2088,58 +2088,58 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.286839</v>
+        <v>-0.286839</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.252789</v>
+        <v>-0.252789</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.227441</v>
+        <v>-0.227441</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.184883</v>
+        <v>-0.184883</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.168084</v>
+        <v>-0.168084</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.184774</v>
+        <v>-0.184774</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.177712</v>
+        <v>-0.177712</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.216566</v>
+        <v>-0.216566</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.161213</v>
+        <v>-0.161213</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.027468</v>
+        <v>-0.027468</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.179918</v>
+        <v>-0.179918</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.616638</v>
+        <v>-0.616638</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.537265</v>
+        <v>-0.537265</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>0.269038</v>
+        <v>-0.269038</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>0.146063</v>
+        <v>-0.146063</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>0.048456</v>
+        <v>-0.048456</v>
       </c>
     </row>
     <row r="28">
@@ -2210,58 +2210,58 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.286839</v>
+        <v>-0.286839</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.252789</v>
+        <v>-0.252789</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.227936</v>
+        <v>-0.226946</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.185324</v>
+        <v>-0.184442</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.168478</v>
+        <v>-0.16769</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.185125</v>
+        <v>-0.184423</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.178025</v>
+        <v>-0.177399</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.216847</v>
+        <v>-0.216285</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.161464</v>
+        <v>-0.160962</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.027468</v>
+        <v>-0.027468</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.179918</v>
+        <v>-0.179918</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.616638</v>
+        <v>-0.616638</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.537265</v>
+        <v>-0.537265</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.269038</v>
+        <v>-0.269038</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.146063</v>
+        <v>-0.146063</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>0.048456</v>
+        <v>-0.048456</v>
       </c>
     </row>
     <row r="30">
@@ -2271,58 +2271,58 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>956129.9999999999</v>
+        <v>-956129.9999999999</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>842629.9999999999</v>
+        <v>-842629.9999999999</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>844207.4074074075</v>
+        <v>-840540.7407407407</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>370648</v>
+        <v>-368884</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>98525.14619883041</v>
+        <v>-98064.32748538011</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>3492.265610262215</v>
+        <v>-3479.022825881909</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>278.5296326428438</v>
+        <v>-277.5502221665936</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>199.8847777593422</v>
+        <v>-199.3667385653448</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>80.80917275998578</v>
+        <v>-80.5579328258487</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.580138846966496</v>
+        <v>-6.580138846966496</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>67.22167407455103</v>
+        <v>-67.22167407455103</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.18213406969916</v>
+        <v>-10.18213406969916</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>21.73295420229073</v>
+        <v>-21.73295420229073</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>71.68058884660184</v>
+        <v>-71.68058884660184</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>64.99854823489559</v>
+        <v>-64.99854823489559</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>34.17557667903503</v>
+        <v>-34.17557667903503</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>18.42431566160805</v>
+        <v>-18.42431566160805</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>5.614838487645988</v>
+        <v>-5.614838487645988</v>
       </c>
     </row>
     <row r="31">
@@ -2332,58 +2332,58 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2393,58 +2393,58 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>956129.9999999999</v>
+        <v>-956129.9999999999</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>842629.9999999999</v>
+        <v>-842629.9999999999</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>842374.074074074</v>
+        <v>-842374.074074074</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>369766</v>
+        <v>-369766</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>98294.73684210527</v>
+        <v>-98294.73684210527</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>3485.644218072062</v>
+        <v>-3485.644218072062</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>278.0399274047187</v>
+        <v>-278.0399274047187</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>199.6257581623435</v>
+        <v>-199.6257581623435</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>80.68355279291724</v>
+        <v>-80.68355279291724</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>6.580138846966496</v>
+        <v>-6.580138846966496</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>67.22167407455103</v>
+        <v>-67.22167407455103</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>10.18213406969916</v>
+        <v>-10.18213406969916</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>21.73295420229073</v>
+        <v>-21.73295420229073</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>71.68058884660184</v>
+        <v>-71.68058884660184</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>64.99854823489559</v>
+        <v>-64.99854823489559</v>
       </c>
       <c r="Q32" s="3" t="n">
-        <v>34.17557667903503</v>
+        <v>-34.17557667903503</v>
       </c>
       <c r="R32" s="3" t="n">
-        <v>18.42431566160805</v>
+        <v>-18.42431566160805</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>5.614838487645988</v>
+        <v>-5.614838487645988</v>
       </c>
     </row>
     <row r="33">
@@ -8460,58 +8460,58 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.286839</v>
+        <v>-0.286839</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.252789</v>
+        <v>-0.252789</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.227441</v>
+        <v>-0.227441</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.184883</v>
+        <v>-0.184883</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.168084</v>
+        <v>-0.168084</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>0.184774</v>
+        <v>-0.184774</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>0.177712</v>
+        <v>-0.177712</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>0.216566</v>
+        <v>-0.216566</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>0.161213</v>
+        <v>-0.161213</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>0.027468</v>
+        <v>-0.027468</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>0.179918</v>
+        <v>-0.179918</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>0.616638</v>
+        <v>-0.616638</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>0.537265</v>
+        <v>-0.537265</v>
       </c>
       <c r="Q99" s="3" t="n">
-        <v>0.269038</v>
+        <v>-0.269038</v>
       </c>
       <c r="R99" s="3" t="n">
-        <v>0.146063</v>
+        <v>-0.146063</v>
       </c>
       <c r="S99" s="3" t="n">
-        <v>0.048456</v>
+        <v>-0.048456</v>
       </c>
     </row>
     <row r="100">
@@ -30770,34 +30770,34 @@
         </is>
       </c>
       <c r="M200" s="5" t="n">
-        <v>0.161213</v>
+        <v>-0.161213</v>
       </c>
       <c r="N200" s="5" t="n">
-        <v>0.027468</v>
+        <v>-0.027468</v>
       </c>
       <c r="O200" s="5" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="P200" s="5" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="Q200" s="5" t="n">
-        <v>0.179918</v>
+        <v>-0.179918</v>
       </c>
       <c r="R200" s="5" t="n">
-        <v>0.616638</v>
+        <v>-0.616638</v>
       </c>
       <c r="S200" s="5" t="n">
-        <v>0.537265</v>
+        <v>-0.537265</v>
       </c>
       <c r="T200" s="5" t="n">
-        <v>0.269038</v>
+        <v>-0.269038</v>
       </c>
       <c r="U200" s="5" t="n">
-        <v>0.146063</v>
+        <v>-0.146063</v>
       </c>
       <c r="V200" s="5" t="n">
-        <v>0.048456</v>
+        <v>-0.048456</v>
       </c>
     </row>
     <row r="201">
@@ -31976,10 +31976,10 @@
         </is>
       </c>
       <c r="O212" s="5" t="n">
-        <v>0.354958</v>
+        <v>-0.354958</v>
       </c>
       <c r="P212" s="5" t="n">
-        <v>0.062943</v>
+        <v>-0.062943</v>
       </c>
       <c r="Q212" t="inlineStr">
         <is>
@@ -34822,25 +34822,25 @@
         </is>
       </c>
       <c r="G240" s="5" t="n">
-        <v>0.227441</v>
+        <v>-0.227441</v>
       </c>
       <c r="H240" s="5" t="n">
-        <v>0.184883</v>
+        <v>-0.184883</v>
       </c>
       <c r="I240" s="5" t="n">
-        <v>0.168084</v>
+        <v>-0.168084</v>
       </c>
       <c r="J240" s="5" t="n">
-        <v>0.184774</v>
+        <v>-0.184774</v>
       </c>
       <c r="K240" s="5" t="n">
-        <v>0.177712</v>
+        <v>-0.177712</v>
       </c>
       <c r="L240" s="5" t="n">
-        <v>0.216566</v>
+        <v>-0.216566</v>
       </c>
       <c r="M240" s="5" t="n">
-        <v>0.143561</v>
+        <v>-0.143561</v>
       </c>
       <c r="N240" t="inlineStr">
         <is>
@@ -37498,13 +37498,13 @@
         </is>
       </c>
       <c r="E266" s="5" t="n">
-        <v>0.286839</v>
+        <v>-0.286839</v>
       </c>
       <c r="F266" s="5" t="n">
-        <v>0.252789</v>
+        <v>-0.252789</v>
       </c>
       <c r="G266" s="5" t="n">
-        <v>0.227441</v>
+        <v>-0.227441</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VPI.xlsx
+++ b/output/pdf_financials_xlsx/VPI.xlsx
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007458</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000305</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1089,28 +1089,28 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003602</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004199</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001668</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002829</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.010201</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007566</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004101</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000489</v>
       </c>
     </row>
     <row r="13">
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.286839</v>
+        <v>-0.294297</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.252789</v>
+        <v>-0.253094</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.227441</v>
@@ -2118,28 +2118,28 @@
         <v>-0.027468</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.354958</v>
+        <v>-0.351356</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.062943</v>
+        <v>-0.058744</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.179918</v>
+        <v>-0.17825</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.616638</v>
+        <v>-0.613809</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.537265</v>
+        <v>-0.527064</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.269038</v>
+        <v>-0.261472</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.146063</v>
+        <v>-0.141962</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>-0.048456</v>
+        <v>-0.047967</v>
       </c>
     </row>
     <row r="28">
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.286839</v>
+        <v>-0.294297</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.252789</v>
+        <v>-0.253094</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.226946</v>
@@ -2240,28 +2240,28 @@
         <v>-0.027468</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.354958</v>
+        <v>-0.351356</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.062943</v>
+        <v>-0.058744</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.179918</v>
+        <v>-0.17825</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.616638</v>
+        <v>-0.613809</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.537265</v>
+        <v>-0.527064</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.269038</v>
+        <v>-0.261472</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.146063</v>
+        <v>-0.141962</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.048456</v>
+        <v>-0.047967</v>
       </c>
     </row>
     <row r="30">
@@ -2271,10 +2271,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-956129.9999999999</v>
+        <v>-980990</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-842629.9999999999</v>
+        <v>-843646.6666666667</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>-840540.7407407407</v>
@@ -2301,28 +2301,28 @@
         <v>-6.580138846966496</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-67.22167407455103</v>
+        <v>-66.53953007436922</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-10.18213406969916</v>
+        <v>-9.502872182616137</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-21.73295420229073</v>
+        <v>-21.53147037293835</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-71.68058884660184</v>
+        <v>-71.35173401467931</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-64.99854823489559</v>
+        <v>-63.76442691572504</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-34.17557667903503</v>
+        <v>-33.21447671117333</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-18.42431566160805</v>
+        <v>-17.90701751951693</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-5.614838487645988</v>
+        <v>-5.558175617816475</v>
       </c>
     </row>
     <row r="31">
@@ -2487,50 +2487,32 @@
       <c r="J34" s="3" t="n">
         <v>0.058832</v>
       </c>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K34" s="3" t="n">
+        <v>0.080467</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.030658</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0.09432500000000001</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0.0366</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0.050981</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>0.069885</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>0.06543</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>0.110847</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>0.121168</v>
       </c>
     </row>
     <row r="35">
@@ -2649,36 +2631,32 @@
       <c r="J36" s="3" t="n">
         <v>0.058832</v>
       </c>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K36" s="3" t="n">
+        <v>0.080467</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.353074</v>
+        <v>0.383732</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.252474</v>
+        <v>0.346799</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.60103</v>
+        <v>0.63763</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0.951815</v>
+        <v>1.002796</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.356377</v>
+        <v>0.426262</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.103227</v>
+        <v>0.168657</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.051676</v>
-      </c>
-      <c r="S36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.162523</v>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>0.121168</v>
       </c>
     </row>
     <row r="37">
@@ -10934,7 +10912,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -30440,7 +30418,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -30536,7 +30514,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -36338,7 +36316,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">
@@ -37386,7 +37364,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E265" s="5" t="n">

--- a/output/pdf_financials_xlsx/VPI.xlsx
+++ b/output/pdf_financials_xlsx/VPI.xlsx
@@ -2176,31 +2176,31 @@
         <v>0.000251</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.000306</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.001815</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.005999</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.008274999999999999</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.043379</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.050392</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.006194</v>
       </c>
       <c r="S28" s="3" t="n">
-        <v>0</v>
+        <v>0.001713</v>
       </c>
     </row>
     <row r="29">
@@ -2237,31 +2237,31 @@
         <v>-0.160962</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.027468</v>
+        <v>-0.027461</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.351356</v>
+        <v>-0.35105</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.058744</v>
+        <v>-0.056929</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.17825</v>
+        <v>-0.172251</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.613809</v>
+        <v>-0.605534</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.527064</v>
+        <v>-0.483685</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.261472</v>
+        <v>-0.21108</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.141962</v>
+        <v>-0.135768</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>-0.047967</v>
+        <v>-0.046254</v>
       </c>
     </row>
     <row r="30">
@@ -2298,31 +2298,31 @@
         <v>-80.5579328258487</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-6.580138846966496</v>
+        <v>-6.578461951235873</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-66.53953007436922</v>
+        <v>-66.48158002882352</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-9.502872182616137</v>
+        <v>-9.209264103298279</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-21.53147037293835</v>
+        <v>-20.80682919051335</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-71.35173401467931</v>
+        <v>-70.38981328857157</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-63.76442691572504</v>
+        <v>-58.51641704372233</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>-33.21447671117333</v>
+        <v>-26.8132409749207</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>-17.90701751951693</v>
+        <v>-17.12570937708524</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>-5.558175617816475</v>
+        <v>-5.359681760929039</v>
       </c>
     </row>
     <row r="31">
@@ -8526,31 +8526,31 @@
         <v>0</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>7e-06</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.000306</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.001815</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.005999</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.008274999999999999</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.043379</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.050392</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.006194</v>
       </c>
       <c r="S100" s="3" t="n">
-        <v>0</v>
+        <v>0.001713</v>
       </c>
     </row>
     <row r="101">
@@ -19004,7 +19004,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VPI.xlsx
+++ b/output/pdf_financials_xlsx/VPI.xlsx
@@ -754,58 +754,58 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.126956</v>
+        <v>0.129756</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.08477</v>
+        <v>0.08967</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.080692</v>
+        <v>0.084892</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.07498</v>
+        <v>0.07673000000000001</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.050328</v>
+        <v>0.052778</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.06162</v>
+        <v>0.06372</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.059199</v>
+        <v>0.060599</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.061881</v>
+        <v>0.064331</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.073894</v>
+        <v>0.07599400000000001</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.09513199999999999</v>
+        <v>0.097232</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.150925</v>
+        <v>0.153375</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.113716</v>
+        <v>0.116166</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.136389</v>
+        <v>0.138839</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.108232</v>
+        <v>0.109982</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.209812</v>
+        <v>0.211912</v>
       </c>
       <c r="Q7" s="3" t="n">
-        <v>0.105762</v>
+        <v>0.107512</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>0.077261</v>
+        <v>0.07866099999999999</v>
       </c>
       <c r="S7" s="3" t="n">
-        <v>0.08286300000000001</v>
+        <v>0.083913</v>
       </c>
     </row>
     <row r="8">
@@ -937,58 +937,58 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.133468</v>
+        <v>0.136268</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.090282</v>
+        <v>0.095182</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.08490499999999999</v>
+        <v>0.089105</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.080224</v>
+        <v>0.08197400000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.053929</v>
+        <v>0.056379</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.066152</v>
+        <v>0.06825199999999999</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.064162</v>
+        <v>0.065562</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.070951</v>
+        <v>0.07340099999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.08809500000000001</v>
+        <v>0.090195</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.112705</v>
+        <v>0.114805</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.178214</v>
+        <v>0.180664</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.143108</v>
+        <v>0.145558</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.163631</v>
+        <v>0.166081</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.136334</v>
+        <v>0.138084</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.259989</v>
+        <v>0.262089</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.142253</v>
+        <v>0.144003</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.101775</v>
+        <v>0.103175</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>0.109214</v>
+        <v>0.110264</v>
       </c>
     </row>
     <row r="11">
@@ -1007,49 +1007,49 @@
         <v>0.227441</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.080223</v>
+        <v>-0.081973</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.053768</v>
+        <v>-0.056218</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.062531</v>
+        <v>-0.06463099999999999</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.024422</v>
+        <v>-0.025822</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.001762</v>
+        <v>-0.000688</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.056085</v>
+        <v>0.053985</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.194433</v>
+        <v>0.192333</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.203651</v>
+        <v>0.201201</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.308308</v>
+        <v>0.305858</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>0.464022</v>
+        <v>0.461572</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>0.496344</v>
+        <v>0.494594</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.346915</v>
+        <v>0.344815</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>0.429026</v>
+        <v>0.427276</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>0.469934</v>
+        <v>0.468534</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>0.51424</v>
+        <v>0.51319</v>
       </c>
     </row>
     <row r="12">
@@ -5179,25 +5179,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0.38336</v>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E64" s="3" t="n">
+        <v>0.017374</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.017374</v>
       </c>
       <c r="G64" s="1" t="inlineStr">
         <is>
@@ -29518,7 +29512,11 @@
           <t>Directors' fees (Note 12)</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -32424,7 +32422,11 @@
           <t>Directors' fees (Note 13)</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -34184,7 +34186,11 @@
           <t>Directors' fees (Note 10)</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -35180,7 +35186,11 @@
           <t>Directors' fees (Note 9)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -36002,7 +36012,11 @@
           <t>Directors' fees</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>0.0028</v>
       </c>
